--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_678_Sao_Tome_Principe.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_678_Sao_Tome_Principe.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R5e1dd0dd628b4f25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rbc8e969193bc480a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R2febfeec897c4d3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R7dd60b4ea2644085"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R73014f919f234c3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rf41f262545c34f6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R6921d2a52f1a4161"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R4000dd13ac0d4196"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rc0ff8b7143fb4b22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R41ca2bdbff774319"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R9ae46270fd864d25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R348752f877064b24"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ678CommercialTable" displayName="EEZ678CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ678CommercialTable" displayName="EEZ678CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ678FunctionalTable" displayName="EEZ678FunctionalTable" ref="A1:O20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O20"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ678FunctionalTable" displayName="EEZ678FunctionalTable" ref="A1:E20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E20"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ678ValidationTable" displayName="EEZ678ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ678ValidationTable" displayName="EEZ678ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -8399,7 +8353,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7f72b295fea4ea5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R730b7c3b69174354"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8409,20 +8363,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -8430,660 +8374,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>0.025778694100000003</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>0.025778694100000003</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$116,A2,'Species'!$U$2:$U$116))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>3.3209391117559433</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>3.3209391117559433</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>0.0064377956</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.91</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>812.8305161640995</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>0.0064377956</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>812.8305161640995</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$116,A3,'Species'!$U$2:$U$116))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>5.232836720506969</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.91</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>812.8305161640995</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>5.232836720506969</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>2.4522370103999998</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.334338235084082</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>215.94255475625965</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>2.4522370103999998</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>257.9890692528979</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$116,A4,'Species'!$U$2:$U$116))</x:f>
-        <x:v>632.6503439006048</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.334338235084082</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>215.94255475625965</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>529.5423248936285</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>103.10801900697629</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.194711572918535</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.194711572918535</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>0.4894375341</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.5769889450679133</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>377.5625799771355</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>0.4894375341</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>379.1290123667465</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$116,A5,'Species'!$U$2:$U$116))</x:f>
-        <x:v>185.55996891854883</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.5769889450679133</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>377.5625799771355</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>184.79329811244324</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0.7666708061055942</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0041488020070894</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.004148802007089508</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>89.9167324417</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.7701224854433866</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>58.90097522114386</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>89.9167324417</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>58.91300786836013</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$116,A6,'Species'!$U$2:$U$116))</x:f>
-        <x:v>5297.265165835105</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.7701224854433866</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>58.90097522114386</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>5296.183229514794</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>1.0819363203108878</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0002042860440101</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.00020428604401022746</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>67.8534848466</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.1000348331610432</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>12.590263896147535</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>67.8534848466</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>12.592798587532643</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$116,A7,'Species'!$U$2:$U$116))</x:f>
-        <x:v>854.4652681354321</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.1000348331610432</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>12.590263896147535</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>854.2932804919418</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0.17198764349029716</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.000201321545443</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.00020132154544310436</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>4488.0837308462005</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.3743188813719414</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>236.76575154767096</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>4488.0837308462005</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>291.46998082972647</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$116,A8,'Species'!$U$2:$U$116))</x:f>
-        <x:v>1308141.6789919492</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.3743188813719414</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>236.76575154767096</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1062624.5175426756</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>245517.16144927358</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.231047898289636</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.23104789828963596</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>3512.6578363686003</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.8772742106736824</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>753.8313776687991</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>3512.6578363686003</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>947.5810407893207</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$116,A9,'Species'!$U$2:$U$116))</x:f>
-        <x:v>3328527.9685229217</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.8772742106736824</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>753.8313776687991</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>2647951.6960688448</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>680576.2724540769</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.2570198971017719</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.2570198971017719</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>225.7627062192</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.7799785254377385</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>602.5297920429412</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>225.7627062192</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>602.5497997517022</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$116,A10,'Species'!$U$2:$U$116))</x:f>
-        <x:v>136033.27342378133</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.7799785254377385</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>602.5297920429412</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>136028.7564293062</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>4.516994475125102</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0000332061734127</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.00003320617341284431</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>340.1028704277</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.3160214298824044</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2070.243500630533</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>340.1028704277</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2212.5706785963926</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$116,A11,'Species'!$U$2:$U$116))</x:f>
-        <x:v>752501.6388147972</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.3160214298824044</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2070.243500630533</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>704095.7570487342</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>48405.88176606293</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.068749003642572</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.06874900364257201</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>2802.9972486813</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.437861139457499</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2740.6977260194903</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>2802.9972486813</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2754.756384877337</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$116,A12,'Species'!$U$2:$U$116))</x:f>
-        <x:v>7721574.56759842</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.437861139457499</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2740.6977260194903</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>7682168.185499727</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>39406.3820986934</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0051295911710283</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.005129591171028236</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac6c3c1bd2ba49e4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc0836c091734473"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9093,20 +8608,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -9114,1092 +8619,383 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>462.0467465608999</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.8090104067587554</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>644.1847015723747</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>462.0467465608999</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>644.4864281412334</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$116,A2,'Species'!$U$2:$U$116))</x:f>
-        <x:v>297782.8573253121</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.8090104067587554</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>644.1847015723747</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>297643.44554581994</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>139.41177949216217</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0004683851822658</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.00046838518226567427</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>176.3398364405</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.8101316405957415</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>645.8499653234303</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>176.3398364405</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>645.9824355852932</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$116,A3,'Species'!$U$2:$U$116))</x:f>
-        <x:v>113912.43703454641</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.8101316405957415</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>645.8499653234303</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>113889.0772502363</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>23.359784310116083</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0002051099620273</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.00020510996202726382</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>3100.9696014803003</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.4267551514693295</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2671.499833608313</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>3100.9696014803003</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2696.8594355338464</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$116,A4,'Species'!$U$2:$U$116))</x:f>
-        <x:v>8362879.129055779</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.4267551514693295</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2671.499833608313</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>8284239.77437906</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>78639.35467671975</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0094926458937041</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.009492645893704124</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>0.051676606800000004</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.61</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>407.3802778041126</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>0.051676606800000004</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>407.3802778041126</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$116,A5,'Species'!$U$2:$U$116))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>21.052030434157896</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.61</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>407.3802778041126</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>21.052030434157896</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>127.52573265160001</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.562150593697503</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>364.88044903994665</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>127.52573265160001</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>366.5074754646589</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$116,A6,'Species'!$U$2:$U$116))</x:f>
-        <x:v>46739.13433091894</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.562150593697503</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>364.88044903994665</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>46531.646594064</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>207.48773685494234</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.004459067151976</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.004459067151975906</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>340.0511938209</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.316128721938681</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2070.755015584208</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>340.0511938209</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2212.8450082156855</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$116,A7,'Species'!$U$2:$U$116))</x:f>
-        <x:v>752480.586784363</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.316128721938681</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2070.755015584208</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>704162.7151600263</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>48317.871624336694</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0686174808522149</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.06861748085221481</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>0.0003264591</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.14</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>138.03842646028852</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>0.0003264591</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>138.03842646028852</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$116,A8,'Species'!$U$2:$U$116))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>0.04506390046764198</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.14</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>138.03842646028852</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>0.04506390046764198</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>0.5546041653</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.390729876187967</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>2458.8377729833187</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>0.5546041653</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2693.00345447574</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$116,A9,'Species'!$U$2:$U$116))</x:f>
-        <x:v>1493.5509330195343</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.390729876187967</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>2458.8377729833187</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>1363.6816706935244</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>129.8692623260099</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0952342948629372</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.09523429486293718</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>2.6976775876000003</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.08</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1202.2644346174131</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>2.6976775876000003</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$116,A10,'Species'!$U$2:$U$116))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>3243.3218196359812</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.08</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>3243.3218196359812</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>334.1184906409</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.5842076382555073</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>383.89074161136205</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>334.1184906409</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>529.8802047239558</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$116,A11,'Species'!$U$2:$U$116))</x:f>
-        <x:v>177042.7742228592</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.5842076382555073</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>383.89074161136205</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>128264.99515820404</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>48777.77906465517</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.3802890960584522</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.3802890960584523</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>4262.690334094499</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.3898313144299697</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>245.3755660268417</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>4262.690334094499</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>290.78730364846683</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$116,A12,'Species'!$U$2:$U$116))</x:f>
-        <x:v>1239536.2285397216</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.3898313144299697</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>245.3755660268417</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>1045960.0535255847</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>193576.17501413682</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.1850703326208833</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.18507033262088327</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>869.6075840786001</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.773623504450704</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>593.7771822461799</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>869.6075840786001</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>929.0866770207252</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$116,A13,'Species'!$U$2:$U$116))</x:f>
-        <x:v>807940.8206036075</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.773623504450704</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>593.7771822461799</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>516353.14093409915</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>291587.6796695083</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.5647059280825075</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.5647059280825076</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>1292.0471661908002</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.916955735009739</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>825.9537608527565</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>1292.0471661908002</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>995.9039094404761</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$116,A14,'Species'!$U$2:$U$116))</x:f>
-        <x:v>1286754.8239909066</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.916955735009739</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>825.9537608527565</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>1067171.216114438</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>219583.60787646868</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.2057623037060266</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.20576230370602658</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>67.8534848466</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.1000348331610432</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>12.590263896147535</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>67.8534848466</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>12.592798587532643</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$116,A15,'Species'!$U$2:$U$116))</x:f>
-        <x:v>854.4652681354321</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.1000348331610432</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>12.590263896147535</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>854.2932804919418</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>0.17198764349029716</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.000201321545443</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.00020132154544310436</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>2.4519105512999997</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.334364110206357</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>215.9554209258675</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>2.4519105512999997</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>258.00504005528694</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$116,A16,'Species'!$U$2:$U$116))</x:f>
-        <x:v>632.6052800001371</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.334364110206357</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>215.9554209258675</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>529.5033751785672</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>103.10190482156986</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.1947143486796477</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.1947143486796477</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>32.7900000001</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.62</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>416.8693834703355</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>32.7900000001</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>416.8693834703355</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$116,A17,'Species'!$U$2:$U$116))</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>13669.147084033988</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.62</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>416.8693834703355</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
-        <x:v>13669.147084033988</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>421.39669897459993</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.422906999401837</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>264.7933044765049</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>421.39669897459993</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>325.72207186640384</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$116,A18,'Species'!$U$2:$U$116))</x:f>
-        <x:v>137258.20586766998</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.422906999401837</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>264.7933044765049</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>111583.02441697531</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>25675.18145069467</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.2300993505494968</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.23009935054949684</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>36.665998181</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.49</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>309.0295432513592</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>36.665998181</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>309.0295432513592</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$116,A19,'Species'!$U$2:$U$116))</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>11330.876670729596</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.49</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>309.0295432513592</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
-        <x:v>11330.876670729596</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>0.4894375341</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.5769889450679133</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>377.5625799771355</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>0.4894375341</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>379.1290123667465</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$116,A20,'Species'!$U$2:$U$116))</x:f>
-        <x:v>185.55996891854883</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.5769889450679133</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>377.5625799771355</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>184.79329811244324</x:v>
       </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>0.7666708061055942</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0041488020070894</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.004148802007089508</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G20">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O20">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc78d66d0da79470d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f07fa3a4af042ca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10374,7 +9170,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -10473,7 +9269,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>13253757.621874493</x:v>
+        <x:v>12239742.278498132</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10487,7 +9283,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>13253757.621874494</x:v>
+        <x:v>12346995.80337172</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10501,7 +9297,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-1014015.3433763608</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10515,7 +9311,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>1.862645149230957e-9</x:v>
+        <x:v>-906761.8185027726</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10526,9 +9322,9 @@
         <x:v>EEZ_678</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -10540,47 +9336,19 @@
         <x:v>EEZ_678</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_678</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_678</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3d723c3f56d4b2e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1f74dc515794aeb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10627,7 +9395,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
